--- a/dist/templates/Code_on_Wages/Form IV - Wage Register.xlsx
+++ b/dist/templates/Code_on_Wages/Form IV - Wage Register.xlsx
@@ -333,7 +333,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -360,18 +360,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2EFDA"/>
-        <bgColor rgb="FFFFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFE2EFDA"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -394,6 +388,13 @@
       </bottom>
       <diagonal/>
     </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -420,76 +421,84 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -538,7 +547,7 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFE2EFDA"/>
+      <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
@@ -748,639 +757,639 @@
   <dimension ref="A1:Y27"/>
   <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="9" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="15" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="18" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="20" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="9" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="15" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="18" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="20" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="1" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
+      <c r="X1" s="2"/>
+      <c r="Y1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
-      <c r="T2" s="2"/>
-      <c r="U2" s="2"/>
-      <c r="V2" s="2"/>
-      <c r="W2" s="2"/>
-      <c r="X2" s="2"/>
-      <c r="Y2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
+      <c r="W2" s="3"/>
+      <c r="X2" s="3"/>
+      <c r="Y2" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="4" t="s">
+      <c r="B4" s="4"/>
+      <c r="C4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="H4" s="5" t="s">
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="H4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="7" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="H5" s="5" t="s">
+      <c r="B5" s="4"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="H5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="6"/>
+      <c r="J5" s="7"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="6" t="s">
+      <c r="B6" s="4"/>
+      <c r="C6" s="7" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="6" t="s">
+      <c r="B7" s="4"/>
+      <c r="C7" s="7" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="I9" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="J9" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="K9" s="7" t="s">
+      <c r="K9" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="L9" s="7" t="s">
+      <c r="L9" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="M9" s="7" t="s">
+      <c r="M9" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="N9" s="7" t="s">
+      <c r="N9" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="O9" s="7" t="s">
+      <c r="O9" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="P9" s="7" t="s">
+      <c r="P9" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="Q9" s="7" t="s">
+      <c r="Q9" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="R9" s="7" t="s">
+      <c r="R9" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="S9" s="7" t="s">
+      <c r="S9" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="T9" s="7" t="s">
+      <c r="T9" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="U9" s="7" t="s">
+      <c r="U9" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="V9" s="7" t="s">
+      <c r="V9" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="W9" s="7" t="s">
+      <c r="W9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="X9" s="7" t="s">
+      <c r="X9" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="Y9" s="7" t="s">
+      <c r="Y9" s="8" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="H11" s="10" t="s">
+      <c r="H11" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="I11" s="10" t="s">
+      <c r="I11" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="J11" s="10" t="s">
+      <c r="J11" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="K11" s="10" t="s">
+      <c r="K11" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="L11" s="10" t="s">
+      <c r="L11" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M11" s="10" t="s">
+      <c r="M11" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="N11" s="8" t="s">
+      <c r="N11" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="O11" s="10" t="s">
+      <c r="O11" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="P11" s="10" t="s">
+      <c r="P11" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="Q11" s="10" t="s">
+      <c r="Q11" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="R11" s="10" t="s">
+      <c r="R11" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="S11" s="10" t="s">
+      <c r="S11" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="T11" s="8" t="s">
+      <c r="T11" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="U11" s="8" t="s">
+      <c r="U11" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="V11" s="8" t="s">
+      <c r="V11" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="W11" s="8"/>
-      <c r="X11" s="8" t="s">
+      <c r="W11" s="9"/>
+      <c r="X11" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="Y11" s="9" t="s">
+      <c r="Y11" s="10" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="11"/>
-      <c r="O12" s="13"/>
-      <c r="P12" s="13"/>
-      <c r="Q12" s="13"/>
-      <c r="R12" s="13"/>
-      <c r="S12" s="13"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
-      <c r="V12" s="11"/>
-      <c r="W12" s="11"/>
-      <c r="X12" s="11"/>
-      <c r="Y12" s="12"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="8"/>
-      <c r="O13" s="10"/>
-      <c r="P13" s="10"/>
-      <c r="Q13" s="10"/>
-      <c r="R13" s="10"/>
-      <c r="S13" s="10"/>
-      <c r="T13" s="8"/>
-      <c r="U13" s="8"/>
-      <c r="V13" s="8"/>
-      <c r="W13" s="8"/>
-      <c r="X13" s="8"/>
-      <c r="Y13" s="9"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="13"/>
-      <c r="M14" s="13"/>
-      <c r="N14" s="11"/>
-      <c r="O14" s="13"/>
-      <c r="P14" s="13"/>
-      <c r="Q14" s="13"/>
-      <c r="R14" s="13"/>
-      <c r="S14" s="13"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
-      <c r="V14" s="11"/>
-      <c r="W14" s="11"/>
-      <c r="X14" s="11"/>
-      <c r="Y14" s="12"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="8"/>
-      <c r="O15" s="10"/>
-      <c r="P15" s="10"/>
-      <c r="Q15" s="10"/>
-      <c r="R15" s="10"/>
-      <c r="S15" s="10"/>
-      <c r="T15" s="8"/>
-      <c r="U15" s="8"/>
-      <c r="V15" s="8"/>
-      <c r="W15" s="8"/>
-      <c r="X15" s="8"/>
-      <c r="Y15" s="9"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="13"/>
-      <c r="L16" s="13"/>
-      <c r="M16" s="13"/>
-      <c r="N16" s="11"/>
-      <c r="O16" s="13"/>
-      <c r="P16" s="13"/>
-      <c r="Q16" s="13"/>
-      <c r="R16" s="13"/>
-      <c r="S16" s="13"/>
-      <c r="T16" s="11"/>
-      <c r="U16" s="11"/>
-      <c r="V16" s="11"/>
-      <c r="W16" s="11"/>
-      <c r="X16" s="11"/>
-      <c r="Y16" s="12"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="8"/>
-      <c r="O17" s="10"/>
-      <c r="P17" s="10"/>
-      <c r="Q17" s="10"/>
-      <c r="R17" s="10"/>
-      <c r="S17" s="10"/>
-      <c r="T17" s="8"/>
-      <c r="U17" s="8"/>
-      <c r="V17" s="8"/>
-      <c r="W17" s="8"/>
-      <c r="X17" s="8"/>
-      <c r="Y17" s="9"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="11"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="13"/>
-      <c r="N18" s="11"/>
-      <c r="O18" s="13"/>
-      <c r="P18" s="13"/>
-      <c r="Q18" s="13"/>
-      <c r="R18" s="13"/>
-      <c r="S18" s="13"/>
-      <c r="T18" s="11"/>
-      <c r="U18" s="11"/>
-      <c r="V18" s="11"/>
-      <c r="W18" s="11"/>
-      <c r="X18" s="11"/>
-      <c r="Y18" s="12"/>
+    <row r="12" s="15" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="12"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="12"/>
+      <c r="O12" s="14"/>
+      <c r="P12" s="14"/>
+      <c r="Q12" s="14"/>
+      <c r="R12" s="14"/>
+      <c r="S12" s="14"/>
+      <c r="T12" s="12"/>
+      <c r="U12" s="12"/>
+      <c r="V12" s="12"/>
+      <c r="W12" s="12"/>
+      <c r="X12" s="12"/>
+      <c r="Y12" s="13"/>
+    </row>
+    <row r="13" s="15" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="12"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="14"/>
+      <c r="N13" s="12"/>
+      <c r="O13" s="14"/>
+      <c r="P13" s="14"/>
+      <c r="Q13" s="14"/>
+      <c r="R13" s="14"/>
+      <c r="S13" s="14"/>
+      <c r="T13" s="12"/>
+      <c r="U13" s="12"/>
+      <c r="V13" s="12"/>
+      <c r="W13" s="12"/>
+      <c r="X13" s="12"/>
+      <c r="Y13" s="13"/>
+    </row>
+    <row r="14" s="15" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="12"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="14"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="14"/>
+      <c r="N14" s="12"/>
+      <c r="O14" s="14"/>
+      <c r="P14" s="14"/>
+      <c r="Q14" s="14"/>
+      <c r="R14" s="14"/>
+      <c r="S14" s="14"/>
+      <c r="T14" s="12"/>
+      <c r="U14" s="12"/>
+      <c r="V14" s="12"/>
+      <c r="W14" s="12"/>
+      <c r="X14" s="12"/>
+      <c r="Y14" s="13"/>
+    </row>
+    <row r="15" s="15" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="12"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="14"/>
+      <c r="L15" s="14"/>
+      <c r="M15" s="14"/>
+      <c r="N15" s="12"/>
+      <c r="O15" s="14"/>
+      <c r="P15" s="14"/>
+      <c r="Q15" s="14"/>
+      <c r="R15" s="14"/>
+      <c r="S15" s="14"/>
+      <c r="T15" s="12"/>
+      <c r="U15" s="12"/>
+      <c r="V15" s="12"/>
+      <c r="W15" s="12"/>
+      <c r="X15" s="12"/>
+      <c r="Y15" s="13"/>
+    </row>
+    <row r="16" s="15" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="12"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="14"/>
+      <c r="L16" s="14"/>
+      <c r="M16" s="14"/>
+      <c r="N16" s="12"/>
+      <c r="O16" s="14"/>
+      <c r="P16" s="14"/>
+      <c r="Q16" s="14"/>
+      <c r="R16" s="14"/>
+      <c r="S16" s="14"/>
+      <c r="T16" s="12"/>
+      <c r="U16" s="12"/>
+      <c r="V16" s="12"/>
+      <c r="W16" s="12"/>
+      <c r="X16" s="12"/>
+      <c r="Y16" s="13"/>
+    </row>
+    <row r="17" s="15" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="12"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="14"/>
+      <c r="M17" s="14"/>
+      <c r="N17" s="12"/>
+      <c r="O17" s="14"/>
+      <c r="P17" s="14"/>
+      <c r="Q17" s="14"/>
+      <c r="R17" s="14"/>
+      <c r="S17" s="14"/>
+      <c r="T17" s="12"/>
+      <c r="U17" s="12"/>
+      <c r="V17" s="12"/>
+      <c r="W17" s="12"/>
+      <c r="X17" s="12"/>
+      <c r="Y17" s="13"/>
+    </row>
+    <row r="18" s="15" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="12"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="14"/>
+      <c r="N18" s="12"/>
+      <c r="O18" s="14"/>
+      <c r="P18" s="14"/>
+      <c r="Q18" s="14"/>
+      <c r="R18" s="14"/>
+      <c r="S18" s="14"/>
+      <c r="T18" s="12"/>
+      <c r="U18" s="12"/>
+      <c r="V18" s="12"/>
+      <c r="W18" s="12"/>
+      <c r="X18" s="12"/>
+      <c r="Y18" s="13"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="15" t="s">
+      <c r="A19" s="16"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14" t="n">
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16" t="n">
         <f aca="false">SUM(H11:H18)</f>
         <v>0</v>
       </c>
-      <c r="I19" s="14" t="n">
+      <c r="I19" s="16" t="n">
         <f aca="false">SUM(I11:I18)</f>
         <v>0</v>
       </c>
-      <c r="J19" s="14" t="n">
+      <c r="J19" s="16" t="n">
         <f aca="false">SUM(J11:J18)</f>
         <v>0</v>
       </c>
-      <c r="K19" s="14" t="n">
+      <c r="K19" s="16" t="n">
         <f aca="false">SUM(K11:K18)</f>
         <v>0</v>
       </c>
-      <c r="L19" s="14" t="n">
+      <c r="L19" s="16" t="n">
         <f aca="false">SUM(L11:L18)</f>
         <v>0</v>
       </c>
-      <c r="M19" s="14" t="n">
+      <c r="M19" s="16" t="n">
         <f aca="false">SUM(M11:M18)</f>
         <v>0</v>
       </c>
-      <c r="N19" s="14" t="n">
+      <c r="N19" s="16" t="n">
         <f aca="false">SUM(N11:N18)</f>
         <v>0</v>
       </c>
-      <c r="O19" s="14" t="n">
+      <c r="O19" s="16" t="n">
         <f aca="false">SUM(O11:O18)</f>
         <v>0</v>
       </c>
-      <c r="P19" s="14" t="n">
+      <c r="P19" s="16" t="n">
         <f aca="false">SUM(P11:P18)</f>
         <v>0</v>
       </c>
-      <c r="Q19" s="14" t="n">
+      <c r="Q19" s="16" t="n">
         <f aca="false">SUM(Q11:Q18)</f>
         <v>0</v>
       </c>
-      <c r="R19" s="14" t="n">
+      <c r="R19" s="16" t="n">
         <f aca="false">SUM(R11:R18)</f>
         <v>0</v>
       </c>
-      <c r="S19" s="14" t="n">
+      <c r="S19" s="16" t="n">
         <f aca="false">SUM(S11:S18)</f>
         <v>0</v>
       </c>
-      <c r="T19" s="14" t="n">
+      <c r="T19" s="16" t="n">
         <f aca="false">SUM(T11:T18)</f>
         <v>0</v>
       </c>
-      <c r="U19" s="14" t="n">
+      <c r="U19" s="16" t="n">
         <f aca="false">SUM(U11:U18)</f>
         <v>0</v>
       </c>
-      <c r="V19" s="14"/>
-      <c r="W19" s="14"/>
-      <c r="X19" s="14"/>
-      <c r="Y19" s="15"/>
+      <c r="V19" s="16"/>
+      <c r="W19" s="16"/>
+      <c r="X19" s="16"/>
+      <c r="Y19" s="17"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="16"/>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="16"/>
-      <c r="O21" s="16"/>
-      <c r="P21" s="16"/>
-      <c r="Q21" s="16"/>
-      <c r="R21" s="16"/>
-      <c r="S21" s="16"/>
-      <c r="T21" s="16"/>
-      <c r="U21" s="16"/>
-      <c r="V21" s="16"/>
-      <c r="W21" s="16"/>
-      <c r="X21" s="16"/>
-      <c r="Y21" s="16"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="18"/>
+      <c r="K21" s="18"/>
+      <c r="L21" s="18"/>
+      <c r="M21" s="18"/>
+      <c r="N21" s="18"/>
+      <c r="O21" s="18"/>
+      <c r="P21" s="18"/>
+      <c r="Q21" s="18"/>
+      <c r="R21" s="18"/>
+      <c r="S21" s="18"/>
+      <c r="T21" s="18"/>
+      <c r="U21" s="18"/>
+      <c r="V21" s="18"/>
+      <c r="W21" s="18"/>
+      <c r="X21" s="18"/>
+      <c r="Y21" s="18"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="16" t="s">
+      <c r="A22" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="16"/>
-      <c r="J22" s="16"/>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="16"/>
-      <c r="O22" s="16"/>
-      <c r="P22" s="16"/>
-      <c r="Q22" s="16"/>
-      <c r="R22" s="16"/>
-      <c r="S22" s="16"/>
-      <c r="T22" s="16"/>
-      <c r="U22" s="16"/>
-      <c r="V22" s="16"/>
-      <c r="W22" s="16"/>
-      <c r="X22" s="16"/>
-      <c r="Y22" s="16"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="18"/>
+      <c r="K22" s="18"/>
+      <c r="L22" s="18"/>
+      <c r="M22" s="18"/>
+      <c r="N22" s="18"/>
+      <c r="O22" s="18"/>
+      <c r="P22" s="18"/>
+      <c r="Q22" s="18"/>
+      <c r="R22" s="18"/>
+      <c r="S22" s="18"/>
+      <c r="T22" s="18"/>
+      <c r="U22" s="18"/>
+      <c r="V22" s="18"/>
+      <c r="W22" s="18"/>
+      <c r="X22" s="18"/>
+      <c r="Y22" s="18"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="H24" s="5" t="s">
+      <c r="H24" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="O24" s="5" t="s">
+      <c r="O24" s="6" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="H25" s="17" t="s">
+      <c r="H25" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="O25" s="17" t="s">
+      <c r="O25" s="19" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="17" t="s">
+      <c r="A26" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="H26" s="17" t="s">
+      <c r="H26" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="O26" s="17" t="s">
+      <c r="O26" s="19" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="H27" s="17" t="s">
+      <c r="H27" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="O27" s="17" t="s">
+      <c r="O27" s="19" t="s">
         <v>69</v>
       </c>
     </row>
